--- a/outputs/consensus_seriation/consensus_seriation.xlsx
+++ b/outputs/consensus_seriation/consensus_seriation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelgreshko/Documents/seriation-new/outputs/consensus_seriation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelgreshko/Documents/GitHub/vms-seriation/outputs/consensus_seriation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157DB047-6C3E-6946-BDBE-00470D514D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4229E28C-9E9B-D142-B716-B727DDE8412E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{F6E16D77-EDEB-9D4B-BCE5-349C8D2A843B}"/>
   </bookViews>
@@ -3781,19 +3781,19 @@
         <v>f105, f114</v>
       </c>
       <c r="H43">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H43,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H43,Sheet2!A:C,3,FALSE))</f>
-        <v>f75, f84</v>
+        <v>f77, f82</v>
       </c>
       <c r="J43">
         <f>VLOOKUP(H43,Sheet2!A:C,2,FALSE)</f>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K43">
         <f>VLOOKUP(H43,Sheet2!A:C,3,FALSE)</f>
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M43" t="s">
         <v>37</v>
@@ -3811,14 +3811,14 @@
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 42&amp;35&amp;f75, f84&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
+        <v xml:space="preserve">    \ 42&amp;37&amp;f77, f82&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
       </c>
       <c r="R43" t="s">
         <v>82</v>
       </c>
       <c r="S43" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 42&amp;f105, f114&amp;f105, f114&amp;f105, f114&amp;f75, f84\\</v>
+        <v xml:space="preserve">    \ 42&amp;f105, f114&amp;f105, f114&amp;f105, f114&amp;f77, f82\\</v>
       </c>
       <c r="W43" t="s">
         <v>140</v>
@@ -3850,19 +3850,19 @@
         <v>f104, f115</v>
       </c>
       <c r="H44">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H44,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H44,Sheet2!A:C,3,FALSE))</f>
-        <v>f78, f81</v>
+        <v>f79, f80</v>
       </c>
       <c r="J44">
         <f>VLOOKUP(H44,Sheet2!A:C,2,FALSE)</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K44">
         <f>VLOOKUP(H44,Sheet2!A:C,3,FALSE)</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M44" t="s">
         <v>37</v>
@@ -3880,14 +3880,14 @@
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 43&amp;38&amp;f78, f81&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
+        <v xml:space="preserve">    \ 43&amp;39&amp;f79, f80&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
       </c>
       <c r="R44" t="s">
         <v>83</v>
       </c>
       <c r="S44" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 43&amp;f104, f115&amp;f104, f115&amp;f104, f115&amp;f78, f81\\</v>
+        <v xml:space="preserve">    \ 43&amp;f104, f115&amp;f104, f115&amp;f104, f115&amp;f79, f80\\</v>
       </c>
       <c r="W44" t="s">
         <v>141</v>
@@ -3919,19 +3919,19 @@
         <v>f106, f113</v>
       </c>
       <c r="H45">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H45,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H45,Sheet2!A:C,3,FALSE))</f>
-        <v>f79, f80</v>
+        <v>f75, f84</v>
       </c>
       <c r="J45">
         <f>VLOOKUP(H45,Sheet2!A:C,2,FALSE)</f>
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K45">
         <f>VLOOKUP(H45,Sheet2!A:C,3,FALSE)</f>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M45" t="s">
         <v>37</v>
@@ -3949,14 +3949,14 @@
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 44&amp;39&amp;f79, f80&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
+        <v xml:space="preserve">    \ 44&amp;35&amp;f75, f84&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
       </c>
       <c r="R45" t="s">
         <v>84</v>
       </c>
       <c r="S45" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 44&amp;f106, f113&amp;f106, f113&amp;f106, f113&amp;f79, f80\\</v>
+        <v xml:space="preserve">    \ 44&amp;f106, f113&amp;f106, f113&amp;f106, f113&amp;f75, f84\\</v>
       </c>
       <c r="W45" t="s">
         <v>142</v>
@@ -3988,19 +3988,19 @@
         <v>f107, f112</v>
       </c>
       <c r="H46">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H46,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H46,Sheet2!A:C,3,FALSE))</f>
-        <v>f77, f82</v>
+        <v>f78, f81</v>
       </c>
       <c r="J46">
         <f>VLOOKUP(H46,Sheet2!A:C,2,FALSE)</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K46">
         <f>VLOOKUP(H46,Sheet2!A:C,3,FALSE)</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M46" t="s">
         <v>37</v>
@@ -4018,14 +4018,14 @@
       </c>
       <c r="Q46" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 45&amp;37&amp;f77, f82&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
+        <v xml:space="preserve">    \ 45&amp;38&amp;f78, f81&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
       </c>
       <c r="R46" t="s">
         <v>85</v>
       </c>
       <c r="S46" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 45&amp;f107, f112&amp;f107, f112&amp;f107, f112&amp;f77, f82\\</v>
+        <v xml:space="preserve">    \ 45&amp;f107, f112&amp;f107, f112&amp;f107, f112&amp;f78, f81\\</v>
       </c>
       <c r="W46" t="s">
         <v>143</v>

--- a/outputs/consensus_seriation/consensus_seriation.xlsx
+++ b/outputs/consensus_seriation/consensus_seriation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelgreshko/Documents/GitHub/vms-seriation/outputs/consensus_seriation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4229E28C-9E9B-D142-B716-B727DDE8412E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F0B2EE-A708-CA41-8F38-4860DF38EEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{F6E16D77-EDEB-9D4B-BCE5-349C8D2A843B}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{F6E16D77-EDEB-9D4B-BCE5-349C8D2A843B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="44">
   <si>
     <t>rank</t>
   </si>
@@ -159,171 +159,6 @@
     <t>Stars</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 1&amp;1&amp;f1, f8&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 2&amp;19&amp;f35, f38&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 3&amp;22&amp;f42, f47&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 4&amp;15&amp;f27, f30&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 5&amp;25&amp;f49, f56&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 6&amp;12&amp;f20, f21&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 7&amp;2&amp;f2, f7&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 8&amp;13&amp;f25, f32&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 9&amp;16&amp;f28, f29&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 10&amp;4&amp;f4, f5&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 11&amp;5&amp;f9, f16&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 12&amp;20&amp;f36, f37&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 13&amp;11&amp;f19, f22&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 14&amp;6&amp;f10, f15&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 15&amp;7&amp;f11, f14&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 16&amp;8&amp;f13, f0&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 17&amp;10&amp;f18, f23&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 18&amp;24&amp;f44, f45&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 19&amp;9&amp;f17, f24&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 20&amp;3&amp;f3, f6&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 21&amp;28&amp;f52, f53&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 22&amp;27&amp;f51, f54&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 23&amp;43&amp;f93, f96&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 24&amp;41&amp;f87, f90&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 25&amp;46&amp;f100, f101&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 26&amp;45&amp;f99, f102&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 27&amp;42&amp;f88, f89&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 28&amp;31&amp;f67, f68&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 29&amp;32&amp;f69, f70&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 30&amp;33&amp;f71, f72&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 31&amp;34&amp;f73, f0&amp;Cosmological/Astrological&amp;-&amp;Bs&amp;4\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 32&amp;30&amp;f58, f65&amp;Cosmological/Astrological&amp;A&amp;A&amp;3\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 33&amp;29&amp;f57, f66&amp;Cosmological/Astrological&amp;B&amp;C&amp;5\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 34&amp;14&amp;f26, f31&amp;Herbal B&amp;B&amp;B&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 35&amp;21&amp;f41, f48&amp;Herbal B&amp;B&amp;B&amp;5\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 36&amp;23&amp;f43, f46&amp;Herbal B&amp;B&amp;Bs&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 37&amp;18&amp;f34, f39&amp;Herbal B&amp;B&amp;B&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 38&amp;17&amp;f33, f40&amp;Herbal B&amp;B&amp;C&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 39&amp;26&amp;f50, f55&amp;Herbal B&amp;B&amp;C&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 40&amp;44&amp;f94, f95&amp;Herbal B&amp;B&amp;B&amp;3\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 41&amp;36&amp;f76, f83&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 42&amp;35&amp;f75, f84&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 43&amp;38&amp;f78, f81&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 44&amp;39&amp;f79, f80&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 45&amp;37&amp;f77, f82&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 46&amp;40&amp;f85, f86&amp;Rosette&amp;B&amp;B&amp;2\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 47&amp;49&amp;f105, f114&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 48&amp;48&amp;f104, f115&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 49&amp;50&amp;f106, f113&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 50&amp;51&amp;f107, f112&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 51&amp;52&amp;f108, f111&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 52&amp;47&amp;f103, f116&amp;Stars&amp;B&amp;B&amp;3\\</t>
-  </si>
-  <si>
-    <t>test_plaintext</t>
-  </si>
-  <si>
-    <t>comp</t>
-  </si>
-  <si>
     <t>hellinger_folia</t>
   </si>
   <si>
@@ -334,162 +169,6 @@
   </si>
   <si>
     <t>consensus_folia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 1&amp;f1, f8&amp;f1, f8&amp;f1, f8&amp;f1, f8\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 2&amp;f35, f38&amp;f35, f38&amp;f35, f38&amp;f35, f38\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 3&amp;f42, f47&amp;f42, f47&amp;f42, f47&amp;f42, f47\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 4&amp;f27, f30&amp;f27, f30&amp;f27, f30&amp;f27, f30\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 5&amp;f49, f56&amp;f49, f56&amp;f2, f7&amp;f49, f56\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 6&amp;f20, f21&amp;f20, f21&amp;f49, f56&amp;f20, f21\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 7&amp;f28, f29&amp;f4, f5&amp;f20, f21&amp;f2, f7\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 8&amp;f25, f32&amp;f28, f29&amp;f25, f32&amp;f25, f32\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 9&amp;f2, f7&amp;f25, f32&amp;f28, f29&amp;f28, f29\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 10&amp;f4, f5&amp;f2, f7&amp;f4, f5&amp;f4, f5\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 11&amp;f3, f6&amp;f10, f15&amp;f88, f89&amp;f9, f16\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 12&amp;f17, f24&amp;f11, f14&amp;f99, f102&amp;f36, f37\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 13&amp;f88, f89&amp;f19, f22&amp;f100, f101&amp;f19, f22\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 14&amp;f99, f102&amp;f36, f37&amp;f87, f90&amp;f10, f15\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 15&amp;f100, f101&amp;f9, f16&amp;f93, f96&amp;f11, f14\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 16&amp;f87, f90&amp;f18, f23&amp;f51, f54&amp;f13, f\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 17&amp;f93, f96&amp;f13, f&amp;f52, f53&amp;f18, f23\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 18&amp;f51, f54&amp;f44, f45&amp;f9, f16&amp;f44, f45\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 19&amp;f52, f53&amp;f17, f24&amp;f36, f37&amp;f17, f24\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 20&amp;f44, f45&amp;f3, f6&amp;f19, f22&amp;f3, f6\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 21&amp;f18, f23&amp;f52, f53&amp;f10, f15&amp;f52, f53\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 22&amp;f13, f&amp;f51, f54&amp;f11, f14&amp;f51, f54\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 23&amp;f11, f14&amp;f93, f96&amp;f13, f&amp;f93, f96\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 24&amp;f10, f15&amp;f87, f90&amp;f18, f23&amp;f87, f90\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 25&amp;f36, f37&amp;f88, f89&amp;f44, f45&amp;f100, f101\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 26&amp;f19, f22&amp;f100, f101&amp;f3, f6&amp;f99, f102\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 27&amp;f9, f16&amp;f99, f102&amp;f17, f24&amp;f88, f89\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 28&amp;f94, f95&amp;f67, f68&amp;f73, f&amp;f67, f68\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 29&amp;f50, f55&amp;f58, f65&amp;f71, f72&amp;f69, f70\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 30&amp;f33, f40&amp;f69, f70&amp;f69, f70&amp;f71, f72\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 31&amp;f34, f39&amp;f71, f72&amp;f58, f65&amp;f73, f\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 32&amp;f43, f46&amp;f73, f&amp;f67, f68&amp;f58, f65\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 33&amp;f41, f48&amp;f57, f66&amp;f57, f66&amp;f57, f66\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 34&amp;f26, f31&amp;f26, f31&amp;f26, f31&amp;f26, f31\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 35&amp;f57, f66&amp;f41, f48&amp;f41, f48&amp;f41, f48\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 36&amp;f67, f68&amp;f43, f46&amp;f43, f46&amp;f43, f46\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 37&amp;f73, f&amp;f34, f39&amp;f34, f39&amp;f34, f39\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 38&amp;f71, f72&amp;f33, f40&amp;f33, f40&amp;f33, f40\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 39&amp;f69, f70&amp;f50, f55&amp;f50, f55&amp;f50, f55\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 40&amp;f58, f65&amp;f94, f95&amp;f94, f95&amp;f94, f95\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 41&amp;f85, f86&amp;f85, f86&amp;f85, f86&amp;f76, f83\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 42&amp;f105, f114&amp;f105, f114&amp;f105, f114&amp;f75, f84\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 43&amp;f104, f115&amp;f104, f115&amp;f104, f115&amp;f78, f81\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 44&amp;f106, f113&amp;f106, f113&amp;f106, f113&amp;f79, f80\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 45&amp;f107, f112&amp;f107, f112&amp;f107, f112&amp;f77, f82\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 46&amp;f108, f111&amp;f108, f111&amp;f108, f111&amp;f85, f86\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 47&amp;f103, f116&amp;f103, f116&amp;f103, f116&amp;f105, f114\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 48&amp;f77, f82&amp;f79, f80&amp;f76, f83&amp;f104, f115\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 49&amp;f76, f83&amp;f77, f82&amp;f78, f81&amp;f106, f113\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 50&amp;f78, f81&amp;f76, f83&amp;f75, f84&amp;f107, f112\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 51&amp;f75, f84&amp;f75, f84&amp;f79, f80&amp;f108, f111\\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    \ 52&amp;f79, f80&amp;f78, f81&amp;f77, f82&amp;f103, f116\\</t>
   </si>
 </sst>
 </file>
@@ -861,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C133D0C-D9B3-3046-8495-A3C87EDA2BD8}">
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="5" width="12.33203125" customWidth="1"/>
@@ -871,7 +550,7 @@
     <col min="18" max="18" width="53.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -879,25 +558,25 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
         <v>23</v>
       </c>
       <c r="E1" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
         <v>22</v>
       </c>
       <c r="G1" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s">
         <v>24</v>
       </c>
       <c r="I1" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s">
         <v>25</v>
@@ -920,17 +599,8 @@
       <c r="P1" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R1" t="s">
-        <v>93</v>
-      </c>
-      <c r="S1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -984,18 +654,8 @@
         <f>VLOOKUP(H2,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="R2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" t="str">
-        <f>_xlfn.CONCAT("    \ ",A2,"&amp;",C2,"&amp;",E2,"&amp;",G2,"&amp;",I2,"\\")</f>
-        <v xml:space="preserve">    \ 1&amp;f1, f8&amp;f1, f8&amp;f1, f8&amp;f1, f8\\</v>
-      </c>
-      <c r="W2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1049,22 +709,8 @@
         <f>VLOOKUP(H3,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q53" si="0">_xlfn.CONCAT("    \ ",A3,"&amp;",H3,"&amp;","f",J3,", f",K3,"&amp;",M3,"&amp;",P3,"&amp;",O3,"&amp;",N3,"\\")</f>
-        <v xml:space="preserve">    \ 2&amp;19&amp;f35, f38&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R3" t="s">
-        <v>42</v>
-      </c>
-      <c r="S3" t="str">
-        <f t="shared" ref="S3:S53" si="1">_xlfn.CONCAT("    \ ",A3,"&amp;",C3,"&amp;",E3,"&amp;",G3,"&amp;",I3,"\\")</f>
-        <v xml:space="preserve">    \ 2&amp;f35, f38&amp;f35, f38&amp;f35, f38&amp;f35, f38\\</v>
-      </c>
-      <c r="W3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1118,22 +764,8 @@
         <f>VLOOKUP(H4,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q4" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 3&amp;22&amp;f42, f47&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R4" t="s">
-        <v>43</v>
-      </c>
-      <c r="S4" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 3&amp;f42, f47&amp;f42, f47&amp;f42, f47&amp;f42, f47\\</v>
-      </c>
-      <c r="W4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1187,22 +819,8 @@
         <f>VLOOKUP(H5,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q5" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 4&amp;15&amp;f27, f30&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R5" t="s">
-        <v>44</v>
-      </c>
-      <c r="S5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 4&amp;f27, f30&amp;f27, f30&amp;f27, f30&amp;f27, f30\\</v>
-      </c>
-      <c r="W5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1256,22 +874,8 @@
         <f>VLOOKUP(H6,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 5&amp;25&amp;f49, f56&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 5&amp;f49, f56&amp;f49, f56&amp;f2, f7&amp;f49, f56\\</v>
-      </c>
-      <c r="W6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1325,22 +929,8 @@
         <f>VLOOKUP(H7,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q7" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 6&amp;12&amp;f20, f21&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S7" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 6&amp;f20, f21&amp;f20, f21&amp;f49, f56&amp;f20, f21\\</v>
-      </c>
-      <c r="W7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1394,22 +984,8 @@
         <f>VLOOKUP(H8,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q8" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 7&amp;2&amp;f2, f7&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R8" t="s">
-        <v>47</v>
-      </c>
-      <c r="S8" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 7&amp;f28, f29&amp;f4, f5&amp;f20, f21&amp;f2, f7\\</v>
-      </c>
-      <c r="W8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1463,22 +1039,8 @@
         <f>VLOOKUP(H9,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q9" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 8&amp;13&amp;f25, f32&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R9" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 8&amp;f25, f32&amp;f28, f29&amp;f25, f32&amp;f25, f32\\</v>
-      </c>
-      <c r="W9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1532,22 +1094,8 @@
         <f>VLOOKUP(H10,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q10" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 9&amp;16&amp;f28, f29&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R10" t="s">
-        <v>49</v>
-      </c>
-      <c r="S10" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 9&amp;f2, f7&amp;f25, f32&amp;f28, f29&amp;f28, f29\\</v>
-      </c>
-      <c r="W10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1601,22 +1149,8 @@
         <f>VLOOKUP(H11,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q11" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 10&amp;4&amp;f4, f5&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R11" t="s">
-        <v>50</v>
-      </c>
-      <c r="S11" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 10&amp;f4, f5&amp;f2, f7&amp;f4, f5&amp;f4, f5\\</v>
-      </c>
-      <c r="W11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1670,22 +1204,8 @@
         <f>VLOOKUP(H12,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q12" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 11&amp;5&amp;f9, f16&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R12" t="s">
-        <v>51</v>
-      </c>
-      <c r="S12" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 11&amp;f3, f6&amp;f10, f15&amp;f88, f89&amp;f9, f16\\</v>
-      </c>
-      <c r="W12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1739,22 +1259,8 @@
         <f>VLOOKUP(H13,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q13" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 12&amp;20&amp;f36, f37&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R13" t="s">
-        <v>52</v>
-      </c>
-      <c r="S13" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 12&amp;f17, f24&amp;f11, f14&amp;f99, f102&amp;f36, f37\\</v>
-      </c>
-      <c r="W13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1808,22 +1314,8 @@
         <f>VLOOKUP(H14,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q14" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 13&amp;11&amp;f19, f22&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R14" t="s">
-        <v>53</v>
-      </c>
-      <c r="S14" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 13&amp;f88, f89&amp;f19, f22&amp;f100, f101&amp;f19, f22\\</v>
-      </c>
-      <c r="W14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1877,22 +1369,8 @@
         <f>VLOOKUP(H15,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q15" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 14&amp;6&amp;f10, f15&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R15" t="s">
-        <v>54</v>
-      </c>
-      <c r="S15" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 14&amp;f99, f102&amp;f36, f37&amp;f87, f90&amp;f10, f15\\</v>
-      </c>
-      <c r="W15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1946,22 +1424,8 @@
         <f>VLOOKUP(H16,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q16" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 15&amp;7&amp;f11, f14&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R16" t="s">
-        <v>55</v>
-      </c>
-      <c r="S16" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 15&amp;f100, f101&amp;f9, f16&amp;f93, f96&amp;f11, f14\\</v>
-      </c>
-      <c r="W16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2015,22 +1479,8 @@
         <f>VLOOKUP(H17,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q17" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 16&amp;8&amp;f13, f0&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R17" t="s">
-        <v>56</v>
-      </c>
-      <c r="S17" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 16&amp;f87, f90&amp;f18, f23&amp;f51, f54&amp;f13, f\\</v>
-      </c>
-      <c r="W17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2084,22 +1534,8 @@
         <f>VLOOKUP(H18,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q18" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 17&amp;10&amp;f18, f23&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R18" t="s">
-        <v>57</v>
-      </c>
-      <c r="S18" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 17&amp;f93, f96&amp;f13, f&amp;f52, f53&amp;f18, f23\\</v>
-      </c>
-      <c r="W18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2153,22 +1589,8 @@
         <f>VLOOKUP(H19,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q19" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 18&amp;24&amp;f44, f45&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R19" t="s">
-        <v>58</v>
-      </c>
-      <c r="S19" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 18&amp;f51, f54&amp;f44, f45&amp;f9, f16&amp;f44, f45\\</v>
-      </c>
-      <c r="W19" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2222,22 +1644,8 @@
         <f>VLOOKUP(H20,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q20" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 19&amp;9&amp;f17, f24&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R20" t="s">
-        <v>59</v>
-      </c>
-      <c r="S20" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 19&amp;f52, f53&amp;f17, f24&amp;f36, f37&amp;f17, f24\\</v>
-      </c>
-      <c r="W20" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2291,22 +1699,8 @@
         <f>VLOOKUP(H21,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q21" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 20&amp;3&amp;f3, f6&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R21" t="s">
-        <v>60</v>
-      </c>
-      <c r="S21" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 20&amp;f44, f45&amp;f3, f6&amp;f19, f22&amp;f3, f6\\</v>
-      </c>
-      <c r="W21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2360,22 +1754,8 @@
         <f>VLOOKUP(H22,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q22" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 21&amp;28&amp;f52, f53&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R22" t="s">
-        <v>61</v>
-      </c>
-      <c r="S22" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 21&amp;f18, f23&amp;f52, f53&amp;f10, f15&amp;f52, f53\\</v>
-      </c>
-      <c r="W22" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2429,22 +1809,8 @@
         <f>VLOOKUP(H23,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q23" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 22&amp;27&amp;f51, f54&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
-      </c>
-      <c r="R23" t="s">
-        <v>62</v>
-      </c>
-      <c r="S23" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 22&amp;f13, f&amp;f51, f54&amp;f11, f14&amp;f51, f54\\</v>
-      </c>
-      <c r="W23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2498,22 +1864,8 @@
         <f>VLOOKUP(H24,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q24" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 23&amp;43&amp;f93, f96&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
-      </c>
-      <c r="R24" t="s">
-        <v>63</v>
-      </c>
-      <c r="S24" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 23&amp;f11, f14&amp;f93, f96&amp;f13, f&amp;f93, f96\\</v>
-      </c>
-      <c r="W24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2567,22 +1919,8 @@
         <f>VLOOKUP(H25,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q25" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 24&amp;41&amp;f87, f90&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
-      </c>
-      <c r="R25" t="s">
-        <v>64</v>
-      </c>
-      <c r="S25" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 24&amp;f10, f15&amp;f87, f90&amp;f18, f23&amp;f87, f90\\</v>
-      </c>
-      <c r="W25" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2636,22 +1974,8 @@
         <f>VLOOKUP(H26,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q26" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 25&amp;46&amp;f100, f101&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
-      </c>
-      <c r="R26" t="s">
-        <v>65</v>
-      </c>
-      <c r="S26" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 25&amp;f36, f37&amp;f88, f89&amp;f44, f45&amp;f100, f101\\</v>
-      </c>
-      <c r="W26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2705,22 +2029,8 @@
         <f>VLOOKUP(H27,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 26&amp;45&amp;f99, f102&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
-      </c>
-      <c r="R27" t="s">
-        <v>66</v>
-      </c>
-      <c r="S27" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 26&amp;f19, f22&amp;f100, f101&amp;f3, f6&amp;f99, f102\\</v>
-      </c>
-      <c r="W27" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2774,22 +2084,8 @@
         <f>VLOOKUP(H28,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q28" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 27&amp;42&amp;f88, f89&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
-      </c>
-      <c r="R28" t="s">
-        <v>67</v>
-      </c>
-      <c r="S28" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 27&amp;f9, f16&amp;f99, f102&amp;f17, f24&amp;f88, f89\\</v>
-      </c>
-      <c r="W28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2843,22 +2139,8 @@
         <f>VLOOKUP(H29,Sheet2!A:G,7,FALSE)</f>
         <v>-</v>
       </c>
-      <c r="Q29" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 28&amp;31&amp;f67, f68&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</v>
-      </c>
-      <c r="R29" t="s">
-        <v>68</v>
-      </c>
-      <c r="S29" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 28&amp;f94, f95&amp;f67, f68&amp;f73, f&amp;f67, f68\\</v>
-      </c>
-      <c r="W29" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2912,22 +2194,8 @@
         <f>VLOOKUP(H30,Sheet2!A:G,7,FALSE)</f>
         <v>-</v>
       </c>
-      <c r="Q30" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 29&amp;32&amp;f69, f70&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</v>
-      </c>
-      <c r="R30" t="s">
-        <v>69</v>
-      </c>
-      <c r="S30" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 29&amp;f50, f55&amp;f58, f65&amp;f71, f72&amp;f69, f70\\</v>
-      </c>
-      <c r="W30" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2981,22 +2249,8 @@
         <f>VLOOKUP(H31,Sheet2!A:G,7,FALSE)</f>
         <v>-</v>
       </c>
-      <c r="Q31" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 30&amp;33&amp;f71, f72&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</v>
-      </c>
-      <c r="R31" t="s">
-        <v>70</v>
-      </c>
-      <c r="S31" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 30&amp;f33, f40&amp;f69, f70&amp;f69, f70&amp;f71, f72\\</v>
-      </c>
-      <c r="W31" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3050,22 +2304,8 @@
         <f>VLOOKUP(H32,Sheet2!A:G,7,FALSE)</f>
         <v>-</v>
       </c>
-      <c r="Q32" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 31&amp;34&amp;f73, f0&amp;Cosmological/Astrological&amp;-&amp;Bs&amp;4\\</v>
-      </c>
-      <c r="R32" t="s">
-        <v>71</v>
-      </c>
-      <c r="S32" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 31&amp;f34, f39&amp;f71, f72&amp;f58, f65&amp;f73, f\\</v>
-      </c>
-      <c r="W32" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3119,22 +2359,8 @@
         <f>VLOOKUP(H33,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-      <c r="Q33" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 32&amp;30&amp;f58, f65&amp;Cosmological/Astrological&amp;A&amp;A&amp;3\\</v>
-      </c>
-      <c r="R33" t="s">
-        <v>72</v>
-      </c>
-      <c r="S33" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 32&amp;f43, f46&amp;f73, f&amp;f67, f68&amp;f58, f65\\</v>
-      </c>
-      <c r="W33" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3188,22 +2414,8 @@
         <f>VLOOKUP(H34,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 33&amp;29&amp;f57, f66&amp;Cosmological/Astrological&amp;B&amp;C&amp;5\\</v>
-      </c>
-      <c r="R34" t="s">
-        <v>73</v>
-      </c>
-      <c r="S34" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 33&amp;f41, f48&amp;f57, f66&amp;f57, f66&amp;f57, f66\\</v>
-      </c>
-      <c r="W34" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3257,22 +2469,8 @@
         <f>VLOOKUP(H35,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q35" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 34&amp;14&amp;f26, f31&amp;Herbal B&amp;B&amp;B&amp;2\\</v>
-      </c>
-      <c r="R35" t="s">
-        <v>74</v>
-      </c>
-      <c r="S35" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 34&amp;f26, f31&amp;f26, f31&amp;f26, f31&amp;f26, f31\\</v>
-      </c>
-      <c r="W35" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3326,22 +2524,8 @@
         <f>VLOOKUP(H36,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q36" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 35&amp;21&amp;f41, f48&amp;Herbal B&amp;B&amp;B&amp;5\\</v>
-      </c>
-      <c r="R36" t="s">
-        <v>75</v>
-      </c>
-      <c r="S36" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 35&amp;f57, f66&amp;f41, f48&amp;f41, f48&amp;f41, f48\\</v>
-      </c>
-      <c r="W36" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3395,22 +2579,8 @@
         <f>VLOOKUP(H37,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q37" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 36&amp;23&amp;f43, f46&amp;Herbal B&amp;B&amp;Bs&amp;2\\</v>
-      </c>
-      <c r="R37" t="s">
-        <v>76</v>
-      </c>
-      <c r="S37" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 36&amp;f67, f68&amp;f43, f46&amp;f43, f46&amp;f43, f46\\</v>
-      </c>
-      <c r="W37" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3464,22 +2634,8 @@
         <f>VLOOKUP(H38,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q38" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 37&amp;18&amp;f34, f39&amp;Herbal B&amp;B&amp;B&amp;2\\</v>
-      </c>
-      <c r="R38" t="s">
-        <v>77</v>
-      </c>
-      <c r="S38" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 37&amp;f73, f&amp;f34, f39&amp;f34, f39&amp;f34, f39\\</v>
-      </c>
-      <c r="W38" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3533,22 +2689,8 @@
         <f>VLOOKUP(H39,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q39" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 38&amp;17&amp;f33, f40&amp;Herbal B&amp;B&amp;C&amp;2\\</v>
-      </c>
-      <c r="R39" t="s">
-        <v>78</v>
-      </c>
-      <c r="S39" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 38&amp;f71, f72&amp;f33, f40&amp;f33, f40&amp;f33, f40\\</v>
-      </c>
-      <c r="W39" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3602,22 +2744,8 @@
         <f>VLOOKUP(H40,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q40" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 39&amp;26&amp;f50, f55&amp;Herbal B&amp;B&amp;C&amp;2\\</v>
-      </c>
-      <c r="R40" t="s">
-        <v>79</v>
-      </c>
-      <c r="S40" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 39&amp;f69, f70&amp;f50, f55&amp;f50, f55&amp;f50, f55\\</v>
-      </c>
-      <c r="W40" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3671,22 +2799,8 @@
         <f>VLOOKUP(H41,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q41" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 40&amp;44&amp;f94, f95&amp;Herbal B&amp;B&amp;B&amp;3\\</v>
-      </c>
-      <c r="R41" t="s">
-        <v>80</v>
-      </c>
-      <c r="S41" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 40&amp;f58, f65&amp;f94, f95&amp;f94, f95&amp;f94, f95\\</v>
-      </c>
-      <c r="W41" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3740,22 +2854,8 @@
         <f>VLOOKUP(H42,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q42" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 41&amp;36&amp;f76, f83&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
-      </c>
-      <c r="R42" t="s">
-        <v>81</v>
-      </c>
-      <c r="S42" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 41&amp;f85, f86&amp;f85, f86&amp;f85, f86&amp;f76, f83\\</v>
-      </c>
-      <c r="W42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3809,22 +2909,8 @@
         <f>VLOOKUP(H43,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q43" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 42&amp;37&amp;f77, f82&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
-      </c>
-      <c r="R43" t="s">
-        <v>82</v>
-      </c>
-      <c r="S43" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 42&amp;f105, f114&amp;f105, f114&amp;f105, f114&amp;f77, f82\\</v>
-      </c>
-      <c r="W43" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3878,22 +2964,8 @@
         <f>VLOOKUP(H44,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q44" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 43&amp;39&amp;f79, f80&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
-      </c>
-      <c r="R44" t="s">
-        <v>83</v>
-      </c>
-      <c r="S44" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 43&amp;f104, f115&amp;f104, f115&amp;f104, f115&amp;f79, f80\\</v>
-      </c>
-      <c r="W44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3947,22 +3019,8 @@
         <f>VLOOKUP(H45,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q45" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 44&amp;35&amp;f75, f84&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
-      </c>
-      <c r="R45" t="s">
-        <v>84</v>
-      </c>
-      <c r="S45" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 44&amp;f106, f113&amp;f106, f113&amp;f106, f113&amp;f75, f84\\</v>
-      </c>
-      <c r="W45" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4016,22 +3074,8 @@
         <f>VLOOKUP(H46,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q46" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 45&amp;38&amp;f78, f81&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
-      </c>
-      <c r="R46" t="s">
-        <v>85</v>
-      </c>
-      <c r="S46" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 45&amp;f107, f112&amp;f107, f112&amp;f107, f112&amp;f78, f81\\</v>
-      </c>
-      <c r="W46" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4085,22 +3129,8 @@
         <f>VLOOKUP(H47,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q47" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 46&amp;40&amp;f85, f86&amp;Rosette&amp;B&amp;B&amp;2\\</v>
-      </c>
-      <c r="R47" t="s">
-        <v>86</v>
-      </c>
-      <c r="S47" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 46&amp;f108, f111&amp;f108, f111&amp;f108, f111&amp;f85, f86\\</v>
-      </c>
-      <c r="W47" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4154,22 +3184,8 @@
         <f>VLOOKUP(H48,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q48" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 47&amp;49&amp;f105, f114&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
-      </c>
-      <c r="R48" t="s">
-        <v>87</v>
-      </c>
-      <c r="S48" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 47&amp;f103, f116&amp;f103, f116&amp;f103, f116&amp;f105, f114\\</v>
-      </c>
-      <c r="W48" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4223,22 +3239,8 @@
         <f>VLOOKUP(H49,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q49" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 48&amp;48&amp;f104, f115&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
-      </c>
-      <c r="R49" t="s">
-        <v>88</v>
-      </c>
-      <c r="S49" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 48&amp;f77, f82&amp;f79, f80&amp;f76, f83&amp;f104, f115\\</v>
-      </c>
-      <c r="W49" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4292,22 +3294,8 @@
         <f>VLOOKUP(H50,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q50" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 49&amp;50&amp;f106, f113&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
-      </c>
-      <c r="R50" t="s">
-        <v>89</v>
-      </c>
-      <c r="S50" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 49&amp;f76, f83&amp;f77, f82&amp;f78, f81&amp;f106, f113\\</v>
-      </c>
-      <c r="W50" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4361,22 +3349,8 @@
         <f>VLOOKUP(H51,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q51" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 50&amp;51&amp;f107, f112&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
-      </c>
-      <c r="R51" t="s">
-        <v>90</v>
-      </c>
-      <c r="S51" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 50&amp;f78, f81&amp;f76, f83&amp;f75, f84&amp;f107, f112\\</v>
-      </c>
-      <c r="W51" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4430,22 +3404,8 @@
         <f>VLOOKUP(H52,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-      <c r="Q52" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 51&amp;52&amp;f108, f111&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
-      </c>
-      <c r="R52" t="s">
-        <v>91</v>
-      </c>
-      <c r="S52" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 51&amp;f75, f84&amp;f75, f84&amp;f79, f80&amp;f108, f111\\</v>
-      </c>
-      <c r="W52" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4498,20 +3458,6 @@
       <c r="P53" t="str">
         <f>VLOOKUP(H53,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
-      </c>
-      <c r="Q53" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 52&amp;47&amp;f103, f116&amp;Stars&amp;B&amp;B&amp;3\\</v>
-      </c>
-      <c r="R53" t="s">
-        <v>92</v>
-      </c>
-      <c r="S53" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 52&amp;f79, f80&amp;f78, f81&amp;f77, f82&amp;f103, f116\\</v>
-      </c>
-      <c r="W53" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/consensus_seriation/consensus_seriation.xlsx
+++ b/outputs/consensus_seriation/consensus_seriation.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F0B2EE-A708-CA41-8F38-4860DF38EEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{F6E16D77-EDEB-9D4B-BCE5-349C8D2A843B}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{F6E16D77-EDEB-9D4B-BCE5-349C8D2A843B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/outputs/consensus_seriation/consensus_seriation.xlsx
+++ b/outputs/consensus_seriation/consensus_seriation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelgreshko/Documents/GitHub/vms-seriation/outputs/consensus_seriation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelgreshko/Documents/vms-seriation/outputs/consensus_seriation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F0B2EE-A708-CA41-8F38-4860DF38EEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4668223-947B-E54E-A7EA-7B35463FEBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{F6E16D77-EDEB-9D4B-BCE5-349C8D2A843B}"/>
+    <workbookView xWindow="5240" yWindow="660" windowWidth="25000" windowHeight="17840" xr2:uid="{F6E16D77-EDEB-9D4B-BCE5-349C8D2A843B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="151">
   <si>
     <t>rank</t>
   </si>
@@ -159,6 +159,171 @@
     <t>Stars</t>
   </si>
   <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 1&amp;1&amp;f1, f8&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 2&amp;19&amp;f35, f38&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 3&amp;22&amp;f42, f47&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 4&amp;15&amp;f27, f30&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 5&amp;25&amp;f49, f56&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 6&amp;12&amp;f20, f21&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 7&amp;2&amp;f2, f7&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 8&amp;13&amp;f25, f32&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 9&amp;16&amp;f28, f29&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 10&amp;4&amp;f4, f5&amp;Herbal A1&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 11&amp;5&amp;f9, f16&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 12&amp;20&amp;f36, f37&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 13&amp;11&amp;f19, f22&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 14&amp;6&amp;f10, f15&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 15&amp;7&amp;f11, f14&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 16&amp;8&amp;f13, f0&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 17&amp;10&amp;f18, f23&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 18&amp;24&amp;f44, f45&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 19&amp;9&amp;f17, f24&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 20&amp;3&amp;f3, f6&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 21&amp;28&amp;f52, f53&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 22&amp;27&amp;f51, f54&amp;Herbal A2&amp;A&amp;A&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 23&amp;43&amp;f93, f96&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 24&amp;41&amp;f87, f90&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 25&amp;46&amp;f100, f101&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 26&amp;45&amp;f99, f102&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 27&amp;42&amp;f88, f89&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 28&amp;31&amp;f67, f68&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 29&amp;32&amp;f69, f70&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 30&amp;33&amp;f71, f72&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 31&amp;34&amp;f73, f0&amp;Cosmological/Astrological&amp;-&amp;Bs&amp;4\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 32&amp;30&amp;f58, f65&amp;Cosmological/Astrological&amp;A&amp;A&amp;3\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 33&amp;29&amp;f57, f66&amp;Cosmological/Astrological&amp;B&amp;C&amp;5\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 34&amp;14&amp;f26, f31&amp;Herbal B&amp;B&amp;B&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 35&amp;21&amp;f41, f48&amp;Herbal B&amp;B&amp;B&amp;5\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 36&amp;23&amp;f43, f46&amp;Herbal B&amp;B&amp;Bs&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 37&amp;18&amp;f34, f39&amp;Herbal B&amp;B&amp;B&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 38&amp;17&amp;f33, f40&amp;Herbal B&amp;B&amp;C&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 39&amp;26&amp;f50, f55&amp;Herbal B&amp;B&amp;C&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 40&amp;44&amp;f94, f95&amp;Herbal B&amp;B&amp;B&amp;3\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 41&amp;36&amp;f76, f83&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 42&amp;35&amp;f75, f84&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 43&amp;38&amp;f78, f81&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 44&amp;39&amp;f79, f80&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 45&amp;37&amp;f77, f82&amp;Biological&amp;B&amp;Bb&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 46&amp;40&amp;f85, f86&amp;Rosette&amp;B&amp;B&amp;2\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 47&amp;49&amp;f105, f114&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 48&amp;48&amp;f104, f115&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 49&amp;50&amp;f106, f113&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 50&amp;51&amp;f107, f112&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 51&amp;52&amp;f108, f111&amp;Stars&amp;B&amp;Bs&amp;3\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 52&amp;47&amp;f103, f116&amp;Stars&amp;B&amp;B&amp;3\\</t>
+  </si>
+  <si>
+    <t>test_plaintext</t>
+  </si>
+  <si>
+    <t>comp</t>
+  </si>
+  <si>
     <t>hellinger_folia</t>
   </si>
   <si>
@@ -169,13 +334,169 @@
   </si>
   <si>
     <t>consensus_folia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 1&amp;f1, f8&amp;f1, f8&amp;f1, f8&amp;f1, f8\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 2&amp;f35, f38&amp;f35, f38&amp;f35, f38&amp;f35, f38\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 3&amp;f42, f47&amp;f42, f47&amp;f42, f47&amp;f42, f47\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 4&amp;f27, f30&amp;f27, f30&amp;f27, f30&amp;f27, f30\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 5&amp;f49, f56&amp;f49, f56&amp;f2, f7&amp;f49, f56\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 6&amp;f20, f21&amp;f20, f21&amp;f49, f56&amp;f20, f21\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 7&amp;f28, f29&amp;f4, f5&amp;f20, f21&amp;f2, f7\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 8&amp;f25, f32&amp;f28, f29&amp;f25, f32&amp;f25, f32\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 9&amp;f2, f7&amp;f25, f32&amp;f28, f29&amp;f28, f29\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 10&amp;f4, f5&amp;f2, f7&amp;f4, f5&amp;f4, f5\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 11&amp;f3, f6&amp;f10, f15&amp;f88, f89&amp;f9, f16\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 12&amp;f17, f24&amp;f11, f14&amp;f99, f102&amp;f36, f37\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 13&amp;f88, f89&amp;f19, f22&amp;f100, f101&amp;f19, f22\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 14&amp;f99, f102&amp;f36, f37&amp;f87, f90&amp;f10, f15\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 15&amp;f100, f101&amp;f9, f16&amp;f93, f96&amp;f11, f14\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 16&amp;f87, f90&amp;f18, f23&amp;f51, f54&amp;f13, f\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 17&amp;f93, f96&amp;f13, f&amp;f52, f53&amp;f18, f23\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 18&amp;f51, f54&amp;f44, f45&amp;f9, f16&amp;f44, f45\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 19&amp;f52, f53&amp;f17, f24&amp;f36, f37&amp;f17, f24\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 20&amp;f44, f45&amp;f3, f6&amp;f19, f22&amp;f3, f6\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 21&amp;f18, f23&amp;f52, f53&amp;f10, f15&amp;f52, f53\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 22&amp;f13, f&amp;f51, f54&amp;f11, f14&amp;f51, f54\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 23&amp;f11, f14&amp;f93, f96&amp;f13, f&amp;f93, f96\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 24&amp;f10, f15&amp;f87, f90&amp;f18, f23&amp;f87, f90\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 25&amp;f36, f37&amp;f88, f89&amp;f44, f45&amp;f100, f101\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 26&amp;f19, f22&amp;f100, f101&amp;f3, f6&amp;f99, f102\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 27&amp;f9, f16&amp;f99, f102&amp;f17, f24&amp;f88, f89\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 28&amp;f94, f95&amp;f67, f68&amp;f73, f&amp;f67, f68\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 29&amp;f50, f55&amp;f58, f65&amp;f71, f72&amp;f69, f70\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 30&amp;f33, f40&amp;f69, f70&amp;f69, f70&amp;f71, f72\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 31&amp;f34, f39&amp;f71, f72&amp;f58, f65&amp;f73, f\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 32&amp;f43, f46&amp;f73, f&amp;f67, f68&amp;f58, f65\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 33&amp;f41, f48&amp;f57, f66&amp;f57, f66&amp;f57, f66\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 34&amp;f26, f31&amp;f26, f31&amp;f26, f31&amp;f26, f31\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 35&amp;f57, f66&amp;f41, f48&amp;f41, f48&amp;f41, f48\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 36&amp;f67, f68&amp;f43, f46&amp;f43, f46&amp;f43, f46\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 37&amp;f73, f&amp;f34, f39&amp;f34, f39&amp;f34, f39\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 38&amp;f71, f72&amp;f33, f40&amp;f33, f40&amp;f33, f40\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 39&amp;f69, f70&amp;f50, f55&amp;f50, f55&amp;f50, f55\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 40&amp;f58, f65&amp;f94, f95&amp;f94, f95&amp;f94, f95\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 41&amp;f85, f86&amp;f85, f86&amp;f85, f86&amp;f76, f83\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 42&amp;f105, f114&amp;f105, f114&amp;f105, f114&amp;f75, f84\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 43&amp;f104, f115&amp;f104, f115&amp;f104, f115&amp;f78, f81\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 44&amp;f106, f113&amp;f106, f113&amp;f106, f113&amp;f79, f80\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 45&amp;f107, f112&amp;f107, f112&amp;f107, f112&amp;f77, f82\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 46&amp;f108, f111&amp;f108, f111&amp;f108, f111&amp;f85, f86\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 47&amp;f103, f116&amp;f103, f116&amp;f103, f116&amp;f105, f114\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 48&amp;f77, f82&amp;f79, f80&amp;f76, f83&amp;f104, f115\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 49&amp;f76, f83&amp;f77, f82&amp;f78, f81&amp;f106, f113\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 50&amp;f78, f81&amp;f76, f83&amp;f75, f84&amp;f107, f112\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 51&amp;f75, f84&amp;f75, f84&amp;f79, f80&amp;f108, f111\\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    \ 52&amp;f79, f80&amp;f78, f81&amp;f77, f82&amp;f103, f116\\</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -183,13 +504,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBACEE8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADC5E4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -204,8 +544,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C133D0C-D9B3-3046-8495-A3C87EDA2BD8}">
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="5" width="12.33203125" customWidth="1"/>
@@ -550,7 +892,7 @@
     <col min="18" max="18" width="53.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,25 +900,25 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
         <v>23</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F1" t="s">
         <v>22</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="H1" t="s">
         <v>24</v>
       </c>
       <c r="I1" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
         <v>25</v>
@@ -599,8 +941,17 @@
       <c r="P1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R1" t="s">
+        <v>93</v>
+      </c>
+      <c r="S1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -654,8 +1005,18 @@
         <f>VLOOKUP(H2,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" t="str">
+        <f>_xlfn.CONCAT("    \ ",A2,"&amp;",C2,"&amp;",E2,"&amp;",G2,"&amp;",I2,"\\")</f>
+        <v xml:space="preserve">    \ 1&amp;f1, f8&amp;f1, f8&amp;f1, f8&amp;f1, f8\\</v>
+      </c>
+      <c r="W2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -709,8 +1070,22 @@
         <f>VLOOKUP(H3,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3:Q53" si="0">_xlfn.CONCAT("    \ ",A3,"&amp;",H3,"&amp;","f",J3,", f",K3,"&amp;",M3,"&amp;",P3,"&amp;",O3,"&amp;",N3,"\\")</f>
+        <v xml:space="preserve">    \ 2&amp;19&amp;f35, f38&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R3" t="s">
+        <v>42</v>
+      </c>
+      <c r="S3" t="str">
+        <f t="shared" ref="S3:S53" si="1">_xlfn.CONCAT("    \ ",A3,"&amp;",C3,"&amp;",E3,"&amp;",G3,"&amp;",I3,"\\")</f>
+        <v xml:space="preserve">    \ 2&amp;f35, f38&amp;f35, f38&amp;f35, f38&amp;f35, f38\\</v>
+      </c>
+      <c r="W3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -764,8 +1139,22 @@
         <f>VLOOKUP(H4,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q4" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 3&amp;22&amp;f42, f47&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 3&amp;f42, f47&amp;f42, f47&amp;f42, f47&amp;f42, f47\\</v>
+      </c>
+      <c r="W4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -819,8 +1208,22 @@
         <f>VLOOKUP(H5,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 4&amp;15&amp;f27, f30&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 4&amp;f27, f30&amp;f27, f30&amp;f27, f30&amp;f27, f30\\</v>
+      </c>
+      <c r="W5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -874,8 +1277,22 @@
         <f>VLOOKUP(H6,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 5&amp;25&amp;f49, f56&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 5&amp;f49, f56&amp;f49, f56&amp;f2, f7&amp;f49, f56\\</v>
+      </c>
+      <c r="W6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -929,8 +1346,22 @@
         <f>VLOOKUP(H7,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 6&amp;12&amp;f20, f21&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S7" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 6&amp;f20, f21&amp;f20, f21&amp;f49, f56&amp;f20, f21\\</v>
+      </c>
+      <c r="W7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -984,8 +1415,22 @@
         <f>VLOOKUP(H8,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 7&amp;2&amp;f2, f7&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R8" t="s">
+        <v>47</v>
+      </c>
+      <c r="S8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 7&amp;f28, f29&amp;f4, f5&amp;f20, f21&amp;f2, f7\\</v>
+      </c>
+      <c r="W8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1039,8 +1484,22 @@
         <f>VLOOKUP(H9,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 8&amp;13&amp;f25, f32&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R9" t="s">
+        <v>48</v>
+      </c>
+      <c r="S9" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 8&amp;f25, f32&amp;f28, f29&amp;f25, f32&amp;f25, f32\\</v>
+      </c>
+      <c r="W9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1094,8 +1553,22 @@
         <f>VLOOKUP(H10,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 9&amp;16&amp;f28, f29&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R10" t="s">
+        <v>49</v>
+      </c>
+      <c r="S10" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 9&amp;f2, f7&amp;f25, f32&amp;f28, f29&amp;f28, f29\\</v>
+      </c>
+      <c r="W10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1149,8 +1622,22 @@
         <f>VLOOKUP(H11,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 10&amp;4&amp;f4, f5&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R11" t="s">
+        <v>50</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 10&amp;f4, f5&amp;f2, f7&amp;f4, f5&amp;f4, f5\\</v>
+      </c>
+      <c r="W11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1204,8 +1691,22 @@
         <f>VLOOKUP(H12,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 11&amp;5&amp;f9, f16&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R12" t="s">
+        <v>51</v>
+      </c>
+      <c r="S12" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 11&amp;f3, f6&amp;f10, f15&amp;f88, f89&amp;f9, f16\\</v>
+      </c>
+      <c r="W12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1259,8 +1760,22 @@
         <f>VLOOKUP(H13,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 12&amp;20&amp;f36, f37&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R13" t="s">
+        <v>52</v>
+      </c>
+      <c r="S13" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 12&amp;f17, f24&amp;f11, f14&amp;f99, f102&amp;f36, f37\\</v>
+      </c>
+      <c r="W13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1314,8 +1829,22 @@
         <f>VLOOKUP(H14,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 13&amp;11&amp;f19, f22&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R14" t="s">
+        <v>53</v>
+      </c>
+      <c r="S14" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 13&amp;f88, f89&amp;f19, f22&amp;f100, f101&amp;f19, f22\\</v>
+      </c>
+      <c r="W14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1369,8 +1898,22 @@
         <f>VLOOKUP(H15,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 14&amp;6&amp;f10, f15&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R15" t="s">
+        <v>54</v>
+      </c>
+      <c r="S15" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 14&amp;f99, f102&amp;f36, f37&amp;f87, f90&amp;f10, f15\\</v>
+      </c>
+      <c r="W15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1424,8 +1967,22 @@
         <f>VLOOKUP(H16,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 15&amp;7&amp;f11, f14&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R16" t="s">
+        <v>55</v>
+      </c>
+      <c r="S16" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 15&amp;f100, f101&amp;f9, f16&amp;f93, f96&amp;f11, f14\\</v>
+      </c>
+      <c r="W16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1479,8 +2036,22 @@
         <f>VLOOKUP(H17,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q17" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 16&amp;8&amp;f13, f0&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R17" t="s">
+        <v>56</v>
+      </c>
+      <c r="S17" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 16&amp;f87, f90&amp;f18, f23&amp;f51, f54&amp;f13, f\\</v>
+      </c>
+      <c r="W17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1534,8 +2105,22 @@
         <f>VLOOKUP(H18,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 17&amp;10&amp;f18, f23&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R18" t="s">
+        <v>57</v>
+      </c>
+      <c r="S18" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 17&amp;f93, f96&amp;f13, f&amp;f52, f53&amp;f18, f23\\</v>
+      </c>
+      <c r="W18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1589,8 +2174,22 @@
         <f>VLOOKUP(H19,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q19" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 18&amp;24&amp;f44, f45&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R19" t="s">
+        <v>58</v>
+      </c>
+      <c r="S19" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 18&amp;f51, f54&amp;f44, f45&amp;f9, f16&amp;f44, f45\\</v>
+      </c>
+      <c r="W19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1644,8 +2243,22 @@
         <f>VLOOKUP(H20,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 19&amp;9&amp;f17, f24&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R20" t="s">
+        <v>59</v>
+      </c>
+      <c r="S20" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 19&amp;f52, f53&amp;f17, f24&amp;f36, f37&amp;f17, f24\\</v>
+      </c>
+      <c r="W20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1699,8 +2312,22 @@
         <f>VLOOKUP(H21,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 20&amp;3&amp;f3, f6&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R21" t="s">
+        <v>60</v>
+      </c>
+      <c r="S21" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 20&amp;f44, f45&amp;f3, f6&amp;f19, f22&amp;f3, f6\\</v>
+      </c>
+      <c r="W21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1754,8 +2381,22 @@
         <f>VLOOKUP(H22,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 21&amp;28&amp;f52, f53&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R22" t="s">
+        <v>61</v>
+      </c>
+      <c r="S22" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 21&amp;f18, f23&amp;f52, f53&amp;f10, f15&amp;f52, f53\\</v>
+      </c>
+      <c r="W22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1809,8 +2450,22 @@
         <f>VLOOKUP(H23,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 22&amp;27&amp;f51, f54&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+      </c>
+      <c r="R23" t="s">
+        <v>62</v>
+      </c>
+      <c r="S23" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 22&amp;f13, f&amp;f51, f54&amp;f11, f14&amp;f51, f54\\</v>
+      </c>
+      <c r="W23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1864,8 +2519,22 @@
         <f>VLOOKUP(H24,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q24" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 23&amp;43&amp;f93, f96&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
+      </c>
+      <c r="R24" t="s">
+        <v>63</v>
+      </c>
+      <c r="S24" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 23&amp;f11, f14&amp;f93, f96&amp;f13, f&amp;f93, f96\\</v>
+      </c>
+      <c r="W24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1919,8 +2588,22 @@
         <f>VLOOKUP(H25,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q25" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 24&amp;41&amp;f87, f90&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
+      </c>
+      <c r="R25" t="s">
+        <v>64</v>
+      </c>
+      <c r="S25" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 24&amp;f10, f15&amp;f87, f90&amp;f18, f23&amp;f87, f90\\</v>
+      </c>
+      <c r="W25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1974,8 +2657,22 @@
         <f>VLOOKUP(H26,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 25&amp;46&amp;f100, f101&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
+      </c>
+      <c r="R26" t="s">
+        <v>65</v>
+      </c>
+      <c r="S26" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 25&amp;f36, f37&amp;f88, f89&amp;f44, f45&amp;f100, f101\\</v>
+      </c>
+      <c r="W26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2029,8 +2726,22 @@
         <f>VLOOKUP(H27,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 26&amp;45&amp;f99, f102&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
+      </c>
+      <c r="R27" t="s">
+        <v>66</v>
+      </c>
+      <c r="S27" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 26&amp;f19, f22&amp;f100, f101&amp;f3, f6&amp;f99, f102\\</v>
+      </c>
+      <c r="W27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2084,8 +2795,22 @@
         <f>VLOOKUP(H28,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q28" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 27&amp;42&amp;f88, f89&amp;Pharmaceutical&amp;A&amp;Ae&amp;1\\</v>
+      </c>
+      <c r="R28" t="s">
+        <v>67</v>
+      </c>
+      <c r="S28" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 27&amp;f9, f16&amp;f99, f102&amp;f17, f24&amp;f88, f89\\</v>
+      </c>
+      <c r="W28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2111,19 +2836,19 @@
         <v>f73, f</v>
       </c>
       <c r="H29">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H29,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H29,Sheet2!A:C,3,FALSE))</f>
-        <v>f67, f68</v>
+        <v>f69, f70</v>
       </c>
       <c r="J29">
         <f>VLOOKUP(H29,Sheet2!A:C,2,FALSE)</f>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K29">
         <f>VLOOKUP(H29,Sheet2!A:C,3,FALSE)</f>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M29" t="s">
         <v>35</v>
@@ -2139,8 +2864,22 @@
         <f>VLOOKUP(H29,Sheet2!A:G,7,FALSE)</f>
         <v>-</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q29" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 28&amp;32&amp;f69, f70&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</v>
+      </c>
+      <c r="R29" t="s">
+        <v>68</v>
+      </c>
+      <c r="S29" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 28&amp;f94, f95&amp;f67, f68&amp;f73, f&amp;f69, f70\\</v>
+      </c>
+      <c r="W29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2166,19 +2905,19 @@
         <v>f71, f72</v>
       </c>
       <c r="H30">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H30,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H30,Sheet2!A:C,3,FALSE))</f>
-        <v>f69, f70</v>
+        <v>f71, f72</v>
       </c>
       <c r="J30">
         <f>VLOOKUP(H30,Sheet2!A:C,2,FALSE)</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K30">
         <f>VLOOKUP(H30,Sheet2!A:C,3,FALSE)</f>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M30" t="s">
         <v>35</v>
@@ -2194,8 +2933,22 @@
         <f>VLOOKUP(H30,Sheet2!A:G,7,FALSE)</f>
         <v>-</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q30" t="str">
+        <f>_xlfn.CONCAT("    \ ",A30,"&amp;",H30,"&amp;","f",J30,", f",K30,"&amp;",M30,"&amp;",P30,"&amp;",O30,"&amp;",N30,"\\")</f>
+        <v xml:space="preserve">    \ 29&amp;33&amp;f71, f72&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</v>
+      </c>
+      <c r="R30" t="s">
+        <v>69</v>
+      </c>
+      <c r="S30" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 29&amp;f50, f55&amp;f58, f65&amp;f71, f72&amp;f71, f72\\</v>
+      </c>
+      <c r="W30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2221,19 +2974,19 @@
         <v>f69, f70</v>
       </c>
       <c r="H31">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H31,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H31,Sheet2!A:C,3,FALSE))</f>
-        <v>f71, f72</v>
+        <v>f73, f</v>
       </c>
       <c r="J31">
         <f>VLOOKUP(H31,Sheet2!A:C,2,FALSE)</f>
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K31">
         <f>VLOOKUP(H31,Sheet2!A:C,3,FALSE)</f>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M31" t="s">
         <v>35</v>
@@ -2243,14 +2996,28 @@
       </c>
       <c r="O31" t="str">
         <f>VLOOKUP(H31,Sheet2!A:G,6,FALSE)</f>
-        <v>Ce</v>
+        <v>Bs</v>
       </c>
       <c r="P31" t="str">
         <f>VLOOKUP(H31,Sheet2!A:G,7,FALSE)</f>
         <v>-</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q31" t="str">
+        <f>_xlfn.CONCAT("    \ ",A31,"&amp;",H31,"&amp;","f",J31,", f",K31,"&amp;",M31,"&amp;",P31,"&amp;",O31,"&amp;",N31,"\\")</f>
+        <v xml:space="preserve">    \ 30&amp;34&amp;f73, f0&amp;Cosmological/Astrological&amp;-&amp;Bs&amp;4\\</v>
+      </c>
+      <c r="R31" t="s">
+        <v>70</v>
+      </c>
+      <c r="S31" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 30&amp;f33, f40&amp;f69, f70&amp;f69, f70&amp;f73, f\\</v>
+      </c>
+      <c r="W31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2276,19 +3043,19 @@
         <v>f58, f65</v>
       </c>
       <c r="H32">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H32,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H32,Sheet2!A:C,3,FALSE))</f>
-        <v>f73, f</v>
+        <v>f67, f68</v>
       </c>
       <c r="J32">
         <f>VLOOKUP(H32,Sheet2!A:C,2,FALSE)</f>
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K32">
         <f>VLOOKUP(H32,Sheet2!A:C,3,FALSE)</f>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M32" t="s">
         <v>35</v>
@@ -2298,14 +3065,28 @@
       </c>
       <c r="O32" t="str">
         <f>VLOOKUP(H32,Sheet2!A:G,6,FALSE)</f>
-        <v>Bs</v>
+        <v>Ce</v>
       </c>
       <c r="P32" t="str">
         <f>VLOOKUP(H32,Sheet2!A:G,7,FALSE)</f>
         <v>-</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q32" t="str">
+        <f>_xlfn.CONCAT("    \ ",A32,"&amp;",H32,"&amp;","f",J32,", f",K32,"&amp;",M32,"&amp;",P32,"&amp;",O32,"&amp;",N32,"\\")</f>
+        <v xml:space="preserve">    \ 31&amp;31&amp;f67, f68&amp;Cosmological/Astrological&amp;-&amp;Ce&amp;4\\</v>
+      </c>
+      <c r="R32" t="s">
+        <v>71</v>
+      </c>
+      <c r="S32" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 31&amp;f34, f39&amp;f71, f72&amp;f58, f65&amp;f67, f68\\</v>
+      </c>
+      <c r="W32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2359,8 +3140,22 @@
         <f>VLOOKUP(H33,Sheet2!A:G,7,FALSE)</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q33" t="str">
+        <f>_xlfn.CONCAT("    \ ",A33,"&amp;",H33,"&amp;","f",J33,", f",K33,"&amp;",M33,"&amp;",P33,"&amp;",O33,"&amp;",N33,"\\")</f>
+        <v xml:space="preserve">    \ 32&amp;30&amp;f58, f65&amp;Cosmological/Astrological&amp;A&amp;A&amp;3\\</v>
+      </c>
+      <c r="R33" t="s">
+        <v>72</v>
+      </c>
+      <c r="S33" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 32&amp;f43, f46&amp;f73, f&amp;f67, f68&amp;f58, f65\\</v>
+      </c>
+      <c r="W33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2414,8 +3209,22 @@
         <f>VLOOKUP(H34,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q34" t="str">
+        <f>_xlfn.CONCAT("    \ ",A34,"&amp;",H34,"&amp;","f",J34,", f",K34,"&amp;",M34,"&amp;",P34,"&amp;",O34,"&amp;",N34,"\\")</f>
+        <v xml:space="preserve">    \ 33&amp;29&amp;f57, f66&amp;Cosmological/Astrological&amp;B&amp;C&amp;5\\</v>
+      </c>
+      <c r="R34" t="s">
+        <v>73</v>
+      </c>
+      <c r="S34" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 33&amp;f41, f48&amp;f57, f66&amp;f57, f66&amp;f57, f66\\</v>
+      </c>
+      <c r="W34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2469,8 +3278,22 @@
         <f>VLOOKUP(H35,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q35" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 34&amp;14&amp;f26, f31&amp;Herbal B&amp;B&amp;B&amp;2\\</v>
+      </c>
+      <c r="R35" t="s">
+        <v>74</v>
+      </c>
+      <c r="S35" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 34&amp;f26, f31&amp;f26, f31&amp;f26, f31&amp;f26, f31\\</v>
+      </c>
+      <c r="W35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2524,8 +3347,22 @@
         <f>VLOOKUP(H36,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q36" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 35&amp;21&amp;f41, f48&amp;Herbal B&amp;B&amp;B&amp;5\\</v>
+      </c>
+      <c r="R36" t="s">
+        <v>75</v>
+      </c>
+      <c r="S36" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 35&amp;f57, f66&amp;f41, f48&amp;f41, f48&amp;f41, f48\\</v>
+      </c>
+      <c r="W36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2579,8 +3416,22 @@
         <f>VLOOKUP(H37,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q37" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 36&amp;23&amp;f43, f46&amp;Herbal B&amp;B&amp;Bs&amp;2\\</v>
+      </c>
+      <c r="R37" t="s">
+        <v>76</v>
+      </c>
+      <c r="S37" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 36&amp;f67, f68&amp;f43, f46&amp;f43, f46&amp;f43, f46\\</v>
+      </c>
+      <c r="W37" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2634,8 +3485,22 @@
         <f>VLOOKUP(H38,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q38" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 37&amp;18&amp;f34, f39&amp;Herbal B&amp;B&amp;B&amp;2\\</v>
+      </c>
+      <c r="R38" t="s">
+        <v>77</v>
+      </c>
+      <c r="S38" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 37&amp;f73, f&amp;f34, f39&amp;f34, f39&amp;f34, f39\\</v>
+      </c>
+      <c r="W38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2689,8 +3554,22 @@
         <f>VLOOKUP(H39,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q39" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 38&amp;17&amp;f33, f40&amp;Herbal B&amp;B&amp;C&amp;2\\</v>
+      </c>
+      <c r="R39" t="s">
+        <v>78</v>
+      </c>
+      <c r="S39" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 38&amp;f71, f72&amp;f33, f40&amp;f33, f40&amp;f33, f40\\</v>
+      </c>
+      <c r="W39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2744,8 +3623,22 @@
         <f>VLOOKUP(H40,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q40" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 39&amp;26&amp;f50, f55&amp;Herbal B&amp;B&amp;C&amp;2\\</v>
+      </c>
+      <c r="R40" t="s">
+        <v>79</v>
+      </c>
+      <c r="S40" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 39&amp;f69, f70&amp;f50, f55&amp;f50, f55&amp;f50, f55\\</v>
+      </c>
+      <c r="W40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2799,8 +3692,22 @@
         <f>VLOOKUP(H41,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q41" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 40&amp;44&amp;f94, f95&amp;Herbal B&amp;B&amp;B&amp;3\\</v>
+      </c>
+      <c r="R41" t="s">
+        <v>80</v>
+      </c>
+      <c r="S41" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 40&amp;f58, f65&amp;f94, f95&amp;f94, f95&amp;f94, f95\\</v>
+      </c>
+      <c r="W41" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2854,8 +3761,22 @@
         <f>VLOOKUP(H42,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q42" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 41&amp;36&amp;f76, f83&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
+      </c>
+      <c r="R42" t="s">
+        <v>81</v>
+      </c>
+      <c r="S42" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 41&amp;f85, f86&amp;f85, f86&amp;f85, f86&amp;f76, f83\\</v>
+      </c>
+      <c r="W42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2909,8 +3830,22 @@
         <f>VLOOKUP(H43,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q43" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 42&amp;37&amp;f77, f82&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
+      </c>
+      <c r="R43" t="s">
+        <v>82</v>
+      </c>
+      <c r="S43" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 42&amp;f105, f114&amp;f105, f114&amp;f105, f114&amp;f77, f82\\</v>
+      </c>
+      <c r="W43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2964,8 +3899,22 @@
         <f>VLOOKUP(H44,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q44" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 43&amp;39&amp;f79, f80&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
+      </c>
+      <c r="R44" t="s">
+        <v>83</v>
+      </c>
+      <c r="S44" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 43&amp;f104, f115&amp;f104, f115&amp;f104, f115&amp;f79, f80\\</v>
+      </c>
+      <c r="W44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2990,7 +3939,7 @@
         <f>_xlfn.CONCAT("f",VLOOKUP(F45,Sheet2!A:C,2,FALSE),", f",VLOOKUP(F45,Sheet2!A:C,3,FALSE))</f>
         <v>f106, f113</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="1">
         <v>35</v>
       </c>
       <c r="I45" t="str">
@@ -3019,8 +3968,22 @@
         <f>VLOOKUP(H45,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q45" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 44&amp;35&amp;f75, f84&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
+      </c>
+      <c r="R45" t="s">
+        <v>84</v>
+      </c>
+      <c r="S45" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 44&amp;f106, f113&amp;f106, f113&amp;f106, f113&amp;f75, f84\\</v>
+      </c>
+      <c r="W45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3045,7 +4008,7 @@
         <f>_xlfn.CONCAT("f",VLOOKUP(F46,Sheet2!A:C,2,FALSE),", f",VLOOKUP(F46,Sheet2!A:C,3,FALSE))</f>
         <v>f107, f112</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="2">
         <v>38</v>
       </c>
       <c r="I46" t="str">
@@ -3074,8 +4037,22 @@
         <f>VLOOKUP(H46,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 45&amp;38&amp;f78, f81&amp;Biological&amp;B&amp;Bb&amp;2\\</v>
+      </c>
+      <c r="R46" t="s">
+        <v>85</v>
+      </c>
+      <c r="S46" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 45&amp;f107, f112&amp;f107, f112&amp;f107, f112&amp;f78, f81\\</v>
+      </c>
+      <c r="W46" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3129,8 +4106,22 @@
         <f>VLOOKUP(H47,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q47" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 46&amp;40&amp;f85, f86&amp;Rosette&amp;B&amp;B&amp;2\\</v>
+      </c>
+      <c r="R47" t="s">
+        <v>86</v>
+      </c>
+      <c r="S47" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 46&amp;f108, f111&amp;f108, f111&amp;f108, f111&amp;f85, f86\\</v>
+      </c>
+      <c r="W47" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3184,8 +4175,22 @@
         <f>VLOOKUP(H48,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q48" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 47&amp;49&amp;f105, f114&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
+      </c>
+      <c r="R48" t="s">
+        <v>87</v>
+      </c>
+      <c r="S48" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 47&amp;f103, f116&amp;f103, f116&amp;f103, f116&amp;f105, f114\\</v>
+      </c>
+      <c r="W48" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3239,8 +4244,22 @@
         <f>VLOOKUP(H49,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q49" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 48&amp;48&amp;f104, f115&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
+      </c>
+      <c r="R49" t="s">
+        <v>88</v>
+      </c>
+      <c r="S49" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 48&amp;f77, f82&amp;f79, f80&amp;f76, f83&amp;f104, f115\\</v>
+      </c>
+      <c r="W49" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3294,8 +4313,22 @@
         <f>VLOOKUP(H50,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q50" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 49&amp;50&amp;f106, f113&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
+      </c>
+      <c r="R50" t="s">
+        <v>89</v>
+      </c>
+      <c r="S50" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 49&amp;f76, f83&amp;f77, f82&amp;f78, f81&amp;f106, f113\\</v>
+      </c>
+      <c r="W50" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3349,8 +4382,22 @@
         <f>VLOOKUP(H51,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q51" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 50&amp;51&amp;f107, f112&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
+      </c>
+      <c r="R51" t="s">
+        <v>90</v>
+      </c>
+      <c r="S51" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 50&amp;f78, f81&amp;f76, f83&amp;f75, f84&amp;f107, f112\\</v>
+      </c>
+      <c r="W51" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3404,8 +4451,22 @@
         <f>VLOOKUP(H52,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q52" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 51&amp;52&amp;f108, f111&amp;Stars&amp;B&amp;Bs&amp;3\\</v>
+      </c>
+      <c r="R52" t="s">
+        <v>91</v>
+      </c>
+      <c r="S52" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 51&amp;f75, f84&amp;f75, f84&amp;f79, f80&amp;f108, f111\\</v>
+      </c>
+      <c r="W52" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3458,6 +4519,20 @@
       <c r="P53" t="str">
         <f>VLOOKUP(H53,Sheet2!A:G,7,FALSE)</f>
         <v>B</v>
+      </c>
+      <c r="Q53" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    \ 52&amp;47&amp;f103, f116&amp;Stars&amp;B&amp;B&amp;3\\</v>
+      </c>
+      <c r="R53" t="s">
+        <v>92</v>
+      </c>
+      <c r="S53" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    \ 52&amp;f79, f80&amp;f78, f81&amp;f77, f82&amp;f103, f116\\</v>
+      </c>
+      <c r="W53" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3473,7 +4548,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:I53">
+  <conditionalFormatting sqref="H2:I44 H47:I53 I45:I46">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
